--- a/output/pdf_financials_xlsx/JZR.xlsx
+++ b/output/pdf_financials_xlsx/JZR.xlsx
@@ -4595,16 +4595,16 @@
         <v>0.956037</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.605844</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.026688</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.211668</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.131001</v>
       </c>
     </row>
     <row r="93">
@@ -7784,7 +7784,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8452,7 +8456,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -8912,7 +8920,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JZR.xlsx
+++ b/output/pdf_financials_xlsx/JZR.xlsx
@@ -1997,28 +1997,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003028</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.008284</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.151742</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.105759</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006081</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022748</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022263</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.082495</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.458237</v>
@@ -2083,28 +2083,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003028</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.008284</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.151742</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.105759</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006081</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022748</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.022263</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.082495</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.458237</v>
@@ -2599,28 +2599,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.232274</v>
+        <v>1.229246</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.058626</v>
+        <v>1.050342</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.220876</v>
+        <v>1.069134</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.114673</v>
+        <v>0.008914</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.010837</v>
+        <v>0.004756</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.027504</v>
+        <v>0.004756</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.022263</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.086987</v>
+        <v>0.004492</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.048099</v>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">

--- a/output/pdf_financials_xlsx/JZR.xlsx
+++ b/output/pdf_financials_xlsx/JZR.xlsx
@@ -5829,16 +5829,16 @@
         </is>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>3.007093</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>1.626937</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>0</v>
+        <v>1.597287</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>1.463876</v>
       </c>
     </row>
     <row r="121">
@@ -13222,7 +13222,11 @@
           <t>Funds received on issuance of common shares net of issuance costs</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JZR.xlsx
+++ b/output/pdf_financials_xlsx/JZR.xlsx
@@ -1132,7 +1132,7 @@
         <v>-0.160065</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.468475</v>
+        <v>-0.328475</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.109833</v>
+        <v>-1.077535</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-1.342326</v>
@@ -1179,7 +1179,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.14</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.032298</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1689,7 +1689,7 @@
         <v>-0.160065</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.468475</v>
+        <v>-0.328475</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.109833</v>
+        <v>-1.077535</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.342326</v>
@@ -1783,7 +1783,7 @@
         <v>-0.160065</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.468475</v>
+        <v>-0.328475</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.109833</v>
+        <v>-1.077535</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.342326</v>
@@ -1897,7 +1897,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-42.62120404901438</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.997396836297661</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -5375,16 +5375,16 @@
         </is>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.255782</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.286432</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.134926</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.18472</v>
       </c>
     </row>
     <row r="111">
@@ -6557,7 +6557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P345"/>
+  <dimension ref="A1:P346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12186,7 +12186,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -13888,7 +13892,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -14648,7 +14656,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -16368,38 +16380,42 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>0.001263</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0.000925</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>0.000677</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>0.000496</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>0.000282</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>0.001072</v>
+          <t>Supplemental disclosure with respect to cash flows (Note</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -16411,10 +16427,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M133" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -16445,37 +16459,31 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Other income on settlement of flow-through premium</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0.001263</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>0.000925</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.000677</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>0.000496</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>0.000282</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>-0.003334</v>
+        <v>0.001072</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -16516,41 +16524,47 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Increase in amounts receivable</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Other income on settlement of flow-through premium</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>-0.005089</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>-0.011699</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>-0.005269</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>-0.004332</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>-0.002634</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>-0.003334</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -16591,12 +16605,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Decrease in prepaid expenses</t>
+          <t>Increase in amounts receivable</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -16605,28 +16619,22 @@
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.004333</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005089</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-0.011699</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>-0.005269</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>0.004158</v>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004332</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>-0.002634</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0.004756</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -16667,30 +16675,42 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Increase in due to related parties</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>0.08105900000000001</v>
+          <t>Decrease in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>-7.2e-05</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>0.01502</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.004333</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I137" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>0.04</v>
+        <v>0.004158</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>0.072452</v>
+        <v>0.004756</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -16731,40 +16751,30 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Increase in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in due to related parties</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>0.08105900000000001</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-7.2e-05</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.01502</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.017203</v>
+        <v>0.003</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>0.061254</v>
+        <v>0.006</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0.004747</v>
+        <v>0.04</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>0.028344</v>
+        <v>0.072452</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -16805,34 +16815,40 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Increase in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="n">
-        <v>-0.100151</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>-0.06790499999999999</v>
-      </c>
-      <c r="G139" s="5" t="n">
-        <v>-0.128695</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>-0.115053</v>
+        <v>0.017203</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>-0.08488999999999999</v>
+        <v>0.061254</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>-0.076672</v>
+        <v>0.004747</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>-0.008607999999999999</v>
+        <v>0.028344</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -16868,45 +16884,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mineral property and deferred exploration costs, net of recoveries</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.100151</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.06790499999999999</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-0.128695</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>-0.115053</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>-0.08488999999999999</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>0.013339</v>
+        <v>-0.076672</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>-0.046877</v>
+        <v>-0.008607999999999999</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -16947,14 +16957,10 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Net cash provided by (used in) investing activities</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Mineral property and deferred exploration costs, net of recoveries</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -17020,17 +17026,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Net cash provided by (used in) investing activities</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -17059,10 +17065,10 @@
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>0.025</v>
+        <v>0.013339</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0.025</v>
+        <v>-0.046877</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -17103,10 +17109,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Advances from related parties</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -17133,12 +17143,10 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -17179,7 +17187,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Repayment of loan</t>
+          <t>Advances from related parties</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -17208,13 +17216,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>-0.04</v>
+      <c r="J144" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -17255,7 +17263,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Loans received</t>
+          <t>Repayment of loan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -17284,11 +17292,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J145" s="5" t="n">
-        <v>0.035</v>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -17329,14 +17339,10 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Loans received</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -17363,10 +17369,10 @@
         </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>0.016667</v>
+        <v>0.035</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>-0.000485</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -17407,12 +17413,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17441,10 +17447,10 @@
         </is>
       </c>
       <c r="J147" s="5" t="n">
-        <v>0.006081</v>
+        <v>0.016667</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>0.022748</v>
+        <v>-0.000485</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -17485,12 +17491,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17519,10 +17525,10 @@
         </is>
       </c>
       <c r="J148" s="5" t="n">
+        <v>0.006081</v>
+      </c>
+      <c r="K148" s="5" t="n">
         <v>0.022748</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0.022263</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -17558,17 +17564,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CASH FLOWS USED IN OPERATING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -17591,16 +17597,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="5" t="n">
-        <v>-0.178376</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>-0.121803</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022748</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>0.022263</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -17636,15 +17642,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS USED IN OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Interest and finance costs</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -17665,13 +17675,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="5" t="n">
+        <v>-0.178376</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>0.00528</v>
+        <v>-0.121803</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -17717,14 +17725,10 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Write-off of amounts receivable</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Interest and finance costs</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -17745,13 +17749,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="5" t="n">
-        <v>0.026124</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>0.00528</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -17792,15 +17796,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mineral property and deferred exploration costs, net of recoveries</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Write-off of amounts receivable</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -17822,10 +17830,12 @@
         </is>
       </c>
       <c r="I152" s="5" t="n">
-        <v>-0.09593599999999999</v>
-      </c>
-      <c r="J152" s="5" t="n">
-        <v>0.013339</v>
+        <v>0.026124</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -17871,7 +17881,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Government subsidies</t>
+          <t>Mineral property and deferred exploration costs, net of recoveries</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -17896,12 +17906,10 @@
         </is>
       </c>
       <c r="I153" s="5" t="n">
-        <v>0.081148</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.09593599999999999</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>0.013339</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -17947,14 +17955,10 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Government subsidies</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -17976,10 +17980,12 @@
         </is>
       </c>
       <c r="I154" s="5" t="n">
-        <v>-0.014788</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>0.013339</v>
+        <v>0.081148</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -18020,17 +18026,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -18053,13 +18059,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="5" t="n">
+        <v>-0.014788</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>0.025</v>
+        <v>0.013339</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -18105,10 +18109,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of flow-through shares</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -18135,7 +18143,7 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -18181,7 +18189,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Loans received</t>
+          <t>Proceeds from issuance of flow-through shares</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -18211,7 +18219,7 @@
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -18257,25 +18265,29 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>0.114382</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>0.1357</v>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>0.391625</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>0.117502</v>
+          <t>Loans received</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -18283,7 +18295,7 @@
         </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>0.08</v>
+        <v>0.035</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -18329,31 +18341,33 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0.002817</v>
+        <v>0.114382</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0.005256</v>
+        <v>0.1357</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.143458</v>
+        <v>0.391625</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>-0.045983</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>-0.099678</v>
+        <v>0.117502</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="5" t="n">
-        <v>0.016667</v>
+        <v>0.08</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -18399,31 +18413,31 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0.000211</v>
+        <v>0.002817</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.003028</v>
+        <v>0.005256</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.008284</v>
+        <v>0.143458</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>0.151742</v>
+        <v>-0.045983</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>0.105759</v>
+        <v>-0.099678</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>0.006081</v>
+        <v>0.016667</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -18469,31 +18483,31 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
+        <v>0.000211</v>
+      </c>
+      <c r="F161" s="5" t="n">
         <v>0.003028</v>
       </c>
-      <c r="F161" s="5" t="n">
+      <c r="G161" s="5" t="n">
         <v>0.008284</v>
       </c>
-      <c r="G161" s="5" t="n">
+      <c r="H161" s="5" t="n">
         <v>0.151742</v>
       </c>
-      <c r="H161" s="5" t="n">
+      <c r="I161" s="5" t="n">
         <v>0.105759</v>
       </c>
-      <c r="I161" s="5" t="n">
+      <c r="J161" s="5" t="n">
         <v>0.006081</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>0.022748</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -18534,42 +18548,36 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.003028</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.008284</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>-0.154158</v>
+        <v>0.151742</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>-0.129236</v>
+        <v>0.105759</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>-0.178376</v>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006081</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>0.022748</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -18610,17 +18618,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Decrease (increase) in prepaid expenses</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -18633,16 +18641,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G163" s="5" t="n">
+        <v>-0.154158</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>-0.001247</v>
+        <v>-0.129236</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>0.004158</v>
+        <v>-0.178376</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -18688,31 +18694,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mineral property and deferred exploration costs, net of recoveries</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Decrease (increase) in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F164" s="5" t="n">
-        <v>-0.066345</v>
-      </c>
-      <c r="G164" s="5" t="n">
-        <v>-0.164959</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H164" s="5" t="n">
-        <v>-0.208278</v>
+        <v>-0.001247</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>-0.09593599999999999</v>
+        <v>0.004158</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -18763,24 +18777,26 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Government subsidies</t>
+          <t>Mineral property and deferred exploration costs, net of recoveries</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>0.004695</v>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0.003806</v>
+        <v>-0.066345</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.045487</v>
+        <v>-0.164959</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0.159846</v>
+        <v>-0.208278</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>0.081148</v>
+        <v>-0.09593599999999999</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -18831,28 +18847,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Government subsidies</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" s="5" t="n">
-        <v>-0.011414</v>
+        <v>0.004695</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.062539</v>
+        <v>0.003806</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>-0.119472</v>
+        <v>0.045487</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>-0.048432</v>
+        <v>0.159846</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>-0.014788</v>
+        <v>0.081148</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -18898,35 +18910,33 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Common shares</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>-0.011414</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>-0.062539</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.325</v>
+        <v>-0.119472</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.048432</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>-0.014788</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -18977,14 +18987,10 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Common shares</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -18996,10 +19002,10 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>-0.008375</v>
+        <v>0.325</v>
       </c>
       <c r="H168" s="5" t="n">
-        <v>-0.005498</v>
+        <v>0.123</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -19050,32 +19056,34 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n">
-        <v>0.002708</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>0.112437</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.038395</v>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008375</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>-0.005498</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -19126,32 +19134,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Increase in prepaid expenses</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>0.002708</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.004333</v>
+        <v>0.112437</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>-0.003334</v>
-      </c>
-      <c r="H170" s="5" t="n">
-        <v>-0.001247</v>
+        <v>0.038395</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -19207,12 +19215,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Increase (decrease) in accounts payable and accrued liabilities</t>
+          <t>Increase in prepaid expenses</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -19220,16 +19228,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F171" s="5" t="n">
+        <v>-0.004333</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>-0.013596</v>
+        <v>-0.003334</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0.017203</v>
+        <v>-0.001247</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -19280,28 +19286,34 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Advances from related parties, net</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>0.114382</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>0.1357</v>
+          <t>Increase (decrease) in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013596</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0.017203</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -19352,27 +19364,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Advances from related parties, net</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" s="5" t="n">
-        <v>-0.16567</v>
+        <v>0.114382</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0.178817</v>
+        <v>0.1357</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>-0.154158</v>
+        <v>0.075</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19428,27 +19436,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gain on debt forgiveness</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>-0.16567</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.339518</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.178817</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>-0.154158</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19504,12 +19512,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Increase (decrease) in due to related parties</t>
+          <t>Gain on debt forgiveness</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -19519,10 +19527,12 @@
         </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-7.2e-05</v>
-      </c>
-      <c r="G175" s="5" t="n">
-        <v>0.01502</v>
+        <v>-0.339518</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -19583,24 +19593,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Decrease (increase) in amounts receivable</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>0.006173</v>
+          <t>Increase (decrease) in due to related parties</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.005089</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-05</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.01502</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -19656,20 +19662,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mineral property and deferred exploration costs</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Decrease (increase) in amounts receivable</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
-        <v>-0.016109</v>
+        <v>0.006173</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>-0.066345</v>
+        <v>-0.005089</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -19725,33 +19735,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Consulting fees 6 $</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Mineral property and deferred exploration costs</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
+        <v>-0.016109</v>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>-0.066345</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -19783,17 +19785,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M178" s="5" t="n">
-        <v>0.188891</v>
-      </c>
-      <c r="N178" s="5" t="n">
-        <v>0.463966</v>
-      </c>
-      <c r="O178" s="5" t="n">
-        <v>0.323661</v>
-      </c>
-      <c r="P178" s="5" t="n">
-        <v>0.550868</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -19809,7 +19819,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Consulting fees 6 $</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -19842,11 +19852,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J179" s="5" t="n">
-        <v>0.018297</v>
-      </c>
-      <c r="K179" s="5" t="n">
-        <v>0.019168</v>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -19854,16 +19868,16 @@
         </is>
       </c>
       <c r="M179" s="5" t="n">
-        <v>0.029313</v>
+        <v>0.188891</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.019803</v>
+        <v>0.463966</v>
       </c>
       <c r="O179" s="5" t="n">
-        <v>0.006108</v>
+        <v>0.323661</v>
       </c>
       <c r="P179" s="5" t="n">
-        <v>0.003918</v>
+        <v>0.550868</v>
       </c>
     </row>
     <row r="180">
@@ -19879,10 +19893,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Interest and charges 7, 8</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -19908,36 +19926,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J180" s="5" t="n">
+        <v>0.018297</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>0.019168</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M180" s="5" t="n">
+        <v>0.029313</v>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>0.019803</v>
       </c>
       <c r="O180" s="5" t="n">
-        <v>0.261531</v>
+        <v>0.006108</v>
       </c>
       <c r="P180" s="5" t="n">
-        <v>0.192936</v>
+        <v>0.003918</v>
       </c>
     </row>
     <row r="181">
@@ -19953,14 +19963,10 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest and charges 7, 8</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -19986,26 +19992,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J181" s="5" t="n">
-        <v>0.016964</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>0.011627</v>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v>0.038522</v>
-      </c>
-      <c r="M181" s="5" t="n">
-        <v>0.110919</v>
-      </c>
-      <c r="N181" s="5" t="n">
-        <v>0.116909</v>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O181" s="5" t="n">
-        <v>0.102508</v>
+        <v>0.261531</v>
       </c>
       <c r="P181" s="5" t="n">
-        <v>0.172702</v>
+        <v>0.192936</v>
       </c>
     </row>
     <row r="182">
@@ -20021,12 +20037,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -20055,25 +20071,25 @@
         </is>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.028124</v>
+        <v>0.016964</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.047631</v>
+        <v>0.011627</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>0.168059</v>
+        <v>0.038522</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>0.13175</v>
+        <v>0.110919</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>0.218923</v>
+        <v>0.116909</v>
       </c>
       <c r="O182" s="5" t="n">
-        <v>0.170997</v>
+        <v>0.102508</v>
       </c>
       <c r="P182" s="5" t="n">
-        <v>0.128466</v>
+        <v>0.172702</v>
       </c>
     </row>
     <row r="183">
@@ -20089,10 +20105,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Share-based compensation 6, 9</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -20118,36 +20138,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J183" s="5" t="n">
+        <v>0.028124</v>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>0.047631</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>0.168059</v>
+      </c>
+      <c r="M183" s="5" t="n">
+        <v>0.13175</v>
+      </c>
+      <c r="N183" s="5" t="n">
+        <v>0.218923</v>
       </c>
       <c r="O183" s="5" t="n">
-        <v>0.187087</v>
+        <v>0.170997</v>
       </c>
       <c r="P183" s="5" t="n">
-        <v>0.047392</v>
+        <v>0.128466</v>
       </c>
     </row>
     <row r="184">
@@ -20163,14 +20173,10 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation 6, 9</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -20201,23 +20207,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K184" s="5" t="n">
-        <v>0.015724</v>
-      </c>
-      <c r="L184" s="5" t="n">
-        <v>0.008447</v>
-      </c>
-      <c r="M184" s="5" t="n">
-        <v>0.06918100000000001</v>
-      </c>
-      <c r="N184" s="5" t="n">
-        <v>0.042126</v>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O184" s="5" t="n">
-        <v>0.038831</v>
+        <v>0.187087</v>
       </c>
       <c r="P184" s="5" t="n">
-        <v>0.067042</v>
+        <v>0.047392</v>
       </c>
     </row>
     <row r="185">
@@ -20233,12 +20247,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Total general and administrative expenses</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -20266,26 +20280,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J185" s="5" t="n">
-        <v>-0.125137</v>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>-0.160065</v>
+        <v>0.015724</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>-0.608475</v>
+        <v>0.008447</v>
       </c>
       <c r="M185" s="5" t="n">
-        <v>1.172551</v>
+        <v>0.06918100000000001</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>1.436889</v>
+        <v>0.042126</v>
       </c>
       <c r="O185" s="5" t="n">
-        <v>1.090723</v>
+        <v>0.038831</v>
       </c>
       <c r="P185" s="5" t="n">
-        <v>1.163324</v>
+        <v>0.067042</v>
       </c>
     </row>
     <row r="186">
@@ -20301,10 +20317,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Accretion expense 7</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Total general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -20330,38 +20350,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J186" s="5" t="n">
+        <v>-0.125137</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>-0.160065</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>-0.608475</v>
+      </c>
+      <c r="M186" s="5" t="n">
+        <v>1.172551</v>
+      </c>
+      <c r="N186" s="5" t="n">
+        <v>1.436889</v>
+      </c>
+      <c r="O186" s="5" t="n">
+        <v>1.090723</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.18472</v>
+        <v>1.163324</v>
       </c>
     </row>
     <row r="187">
@@ -20377,7 +20385,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Settlement of litigation</t>
+          <t>Accretion expense 7</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -20431,13 +20439,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O187" s="5" t="n">
-        <v>0.056488</v>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P187" s="5" t="n">
+        <v>0.18472</v>
       </c>
     </row>
     <row r="188">
@@ -20453,7 +20461,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Interest revenue 4</t>
+          <t>Settlement of litigation</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -20502,14 +20510,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N188" s="5" t="n">
-        <v>-0.001354</v>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O188" s="5" t="n">
-        <v>-0.00508</v>
-      </c>
-      <c r="P188" s="5" t="n">
-        <v>-0.005718</v>
+        <v>0.056488</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -20525,10 +20537,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss before income tax</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Interest revenue 4</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -20569,17 +20585,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M189" s="5" t="n">
-        <v>-2.362109</v>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N189" s="5" t="n">
-        <v>-1.320323</v>
+        <v>-0.001354</v>
       </c>
       <c r="O189" s="5" t="n">
-        <v>-1.142131</v>
+        <v>-0.00508</v>
       </c>
       <c r="P189" s="5" t="n">
-        <v>-1.342326</v>
+        <v>-0.005718</v>
       </c>
     </row>
     <row r="190">
@@ -20595,7 +20613,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Income tax recovery 9</t>
+          <t>Loss and comprehensive loss before income tax</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -20639,23 +20657,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M190" s="5" t="n">
+        <v>-2.362109</v>
+      </c>
+      <c r="N190" s="5" t="n">
+        <v>-1.320323</v>
       </c>
       <c r="O190" s="5" t="n">
-        <v>0.032298</v>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.142131</v>
+      </c>
+      <c r="P190" s="5" t="n">
+        <v>-1.342326</v>
       </c>
     </row>
     <row r="191">
@@ -20671,12 +20683,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Income tax recovery 9</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -20704,26 +20716,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J191" s="5" t="n">
-        <v>-0.121803</v>
-      </c>
-      <c r="K191" s="5" t="n">
-        <v>-0.160065</v>
-      </c>
-      <c r="L191" s="5" t="n">
-        <v>-0.468475</v>
-      </c>
-      <c r="M191" s="5" t="n">
-        <v>-2.350109</v>
-      </c>
-      <c r="N191" s="5" t="n">
-        <v>-1.320323</v>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O191" s="5" t="n">
-        <v>-1.109833</v>
-      </c>
-      <c r="P191" s="5" t="n">
-        <v>-1.342326</v>
+        <v>0.032298</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -20739,12 +20763,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -20773,25 +20797,25 @@
         </is>
       </c>
       <c r="J192" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-0.121803</v>
       </c>
       <c r="K192" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.160065</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.468475</v>
       </c>
       <c r="M192" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-2.350109</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-1.320323</v>
       </c>
       <c r="O192" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.109833</v>
       </c>
       <c r="P192" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.342326</v>
       </c>
     </row>
     <row r="193">
@@ -20807,10 +20831,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -20836,36 +20864,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J193" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="M193" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="N193" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="O193" s="5" t="n">
-        <v>42.089523</v>
+        <v>-3e-08</v>
       </c>
       <c r="P193" s="5" t="n">
-        <v>52.941502</v>
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="194">
@@ -20881,7 +20899,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -20930,16 +20948,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N194" s="5" t="n">
-        <v>0.463966</v>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O194" s="5" t="n">
-        <v>0.323661</v>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>42.089523</v>
+      </c>
+      <c r="P194" s="5" t="n">
+        <v>52.941502</v>
       </c>
     </row>
     <row r="195">
@@ -20955,7 +20973,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Interest and charges</t>
+          <t>Consulting fees $</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -21005,10 +21023,10 @@
         </is>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.180339</v>
+        <v>0.463966</v>
       </c>
       <c r="O195" s="5" t="n">
-        <v>0.261531</v>
+        <v>0.323661</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -21029,7 +21047,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Interest and charges</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -21079,10 +21097,10 @@
         </is>
       </c>
       <c r="N196" s="5" t="n">
-        <v>0.394823</v>
+        <v>0.180339</v>
       </c>
       <c r="O196" s="5" t="n">
-        <v>0.187087</v>
+        <v>0.261531</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -21103,7 +21121,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Accretion expense</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -21153,12 +21171,10 @@
         </is>
       </c>
       <c r="N197" s="5" t="n">
-        <v>0.286432</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.394823</v>
+      </c>
+      <c r="O197" s="5" t="n">
+        <v>0.187087</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -21179,7 +21195,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties and deferred exploration costs</t>
+          <t>Accretion expense</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -21229,7 +21245,7 @@
         </is>
       </c>
       <c r="N198" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.286432</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -21255,7 +21271,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of accounts payable</t>
+          <t>Impairment of mineral properties and deferred exploration costs</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -21305,7 +21321,7 @@
         </is>
       </c>
       <c r="N199" s="5" t="n">
-        <v>-0.485691</v>
+        <v>1e-06</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -21331,7 +21347,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Loss on sale of mineral property rights</t>
+          <t>Gain on extinguishment of accounts payable</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -21381,7 +21397,7 @@
         </is>
       </c>
       <c r="N200" s="5" t="n">
-        <v>0.084046</v>
+        <v>-0.485691</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -21407,7 +21423,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Interest revenue</t>
+          <t>Loss on sale of mineral property rights</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -21457,10 +21473,12 @@
         </is>
       </c>
       <c r="N201" s="5" t="n">
-        <v>-0.001354</v>
-      </c>
-      <c r="O201" s="5" t="n">
-        <v>-0.00508</v>
+        <v>0.084046</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
@@ -21481,7 +21499,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Interest revenue</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -21530,13 +21548,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N202" s="5" t="n">
+        <v>-0.001354</v>
       </c>
       <c r="O202" s="5" t="n">
-        <v>0.032298</v>
+        <v>-0.00508</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -21552,12 +21568,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Income tax recovery</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -21606,11 +21622,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N203" s="5" t="n">
-        <v>30.802797</v>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O203" s="5" t="n">
-        <v>42.089523</v>
+        <v>0.032298</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
@@ -21626,12 +21644,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Reserve                       Debentures</t>
+          <t>Weighted average number of common shares outstanding –</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2022 28,567,266 $ 13,171,433 $ (90,651) $ 1,433,900 $ 171,944 $ 417,686 $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -21681,10 +21699,10 @@
         </is>
       </c>
       <c r="N204" s="5" t="n">
-        <v>6.8361</v>
+        <v>30.802797</v>
       </c>
       <c r="O204" s="5" t="n">
-        <v>-8.268212</v>
+        <v>42.089523</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -21705,7 +21723,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Units issued in private placement 9 2,610,018 1,571,632 (19,000) - 81,130 -</t>
+          <t>Balance, June 30, 2022 28,567,266 $ 13,171,433 $ (90,651) $ 1,433,900 $ 171,944 $ 417,686 $</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -21755,12 +21773,10 @@
         </is>
       </c>
       <c r="N205" s="5" t="n">
-        <v>1.633762</v>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.8361</v>
+      </c>
+      <c r="O205" s="5" t="n">
+        <v>-8.268212</v>
       </c>
       <c r="P205" t="inlineStr">
         <is>
@@ -21781,7 +21797,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Share issuance costs 9 - (6,825) - - - -</t>
+          <t>Units issued in private placement 9 2,610,018 1,571,632 (19,000) - 81,130 -</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -21831,7 +21847,7 @@
         </is>
       </c>
       <c r="N206" s="5" t="n">
-        <v>-0.006825</v>
+        <v>1.633762</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -21857,7 +21873,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Equity portion of convertible debenture - 417,686 - - - (417,686)</t>
+          <t>Share issuance costs 9 - (6,825) - - - -</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -21906,10 +21922,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N207" s="5" t="n">
+        <v>-0.006825</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -21935,7 +21949,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of convertible debenture 6,583,333 1,975,000 - - - -</t>
+          <t>Equity portion of convertible debenture - 417,686 - - - (417,686)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -21984,8 +21998,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N208" s="5" t="n">
-        <v>1.975</v>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -22011,7 +22027,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Broker warrants in connection with private placement 9 - (2,013) - - 2,013 -</t>
+          <t>Shares issued on conversion of convertible debenture 6,583,333 1,975,000 - - - -</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -22060,10 +22076,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N209" s="5" t="n">
+        <v>1.975</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -22089,7 +22103,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Expiry of broker warrants 9 - 26,118 - - (26,118) -</t>
+          <t>Broker warrants in connection with private placement 9 - (2,013) - - 2,013 -</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -22167,7 +22181,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Share-based compensation 9 - - - 394,823 - -</t>
+          <t>Expiry of broker warrants 9 - 26,118 - - (26,118) -</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -22216,8 +22230,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N211" s="5" t="n">
-        <v>0.394823</v>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -22243,7 +22259,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Exercise of options 9 250,000 118,504 - (31,004) - -</t>
+          <t>Share-based compensation 9 - - - 394,823 - -</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -22293,7 +22309,7 @@
         </is>
       </c>
       <c r="N212" s="5" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.394823</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -22319,7 +22335,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Exercise of warrants 9 20,000 6,000 - - - -</t>
+          <t>Exercise of options 9 250,000 118,504 - (31,004) - -</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -22369,7 +22385,7 @@
         </is>
       </c>
       <c r="N213" s="5" t="n">
-        <v>0.006</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -22395,7 +22411,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - -</t>
+          <t>Exercise of warrants 9 20,000 6,000 - - - -</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -22445,10 +22461,12 @@
         </is>
       </c>
       <c r="N214" s="5" t="n">
-        <v>-1.320323</v>
-      </c>
-      <c r="O214" s="5" t="n">
-        <v>-1.320323</v>
+        <v>0.006</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
@@ -22469,7 +22487,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 38,030,617 $ 17,277,535 $ (109,651) $ 1,797,719 $ 228,969 $ - $</t>
+          <t>Net loss and comprehensive loss for the year - - - - - -</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -22519,10 +22537,10 @@
         </is>
       </c>
       <c r="N215" s="5" t="n">
-        <v>9.606037000000001</v>
+        <v>-1.320323</v>
       </c>
       <c r="O215" s="5" t="n">
-        <v>-9.588535</v>
+        <v>-1.320323</v>
       </c>
       <c r="P215" t="inlineStr">
         <is>
@@ -22543,7 +22561,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Units issued in private placement 9 9,302,666 1,565,400 39,085 - - -</t>
+          <t>Balance, June 30, 2023 38,030,617 $ 17,277,535 $ (109,651) $ 1,797,719 $ 228,969 $ - $</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -22593,12 +22611,10 @@
         </is>
       </c>
       <c r="N216" s="5" t="n">
-        <v>1.604485</v>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.606037000000001</v>
+      </c>
+      <c r="O216" s="5" t="n">
+        <v>-9.588535</v>
       </c>
       <c r="P216" t="inlineStr">
         <is>
@@ -22619,7 +22635,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Share issuance costs 9 - (7,200) - - - -</t>
+          <t>Units issued in private placement 9 9,302,666 1,565,400 39,085 - - -</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -22669,7 +22685,7 @@
         </is>
       </c>
       <c r="N217" s="5" t="n">
-        <v>-0.0072</v>
+        <v>1.604485</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -22695,7 +22711,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bonus shares issued in connection with short term loans 8,9 300,000 144,000 - - - -</t>
+          <t>Share issuance costs 9 - (7,200) - - - -</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -22745,7 +22761,7 @@
         </is>
       </c>
       <c r="N218" s="5" t="n">
-        <v>0.144</v>
+        <v>-0.0072</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -22771,7 +22787,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Broker warrants in connection with private placement 9 - 4,120 - - (4,120) -</t>
+          <t>Bonus shares issued in connection with short term loans 8,9 300,000 144,000 - - - -</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -22820,10 +22836,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N219" s="5" t="n">
+        <v>0.144</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -22849,7 +22863,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Expiry of broker warrants 9 - (2,013) - - 2,013 -</t>
+          <t>Broker warrants in connection with private placement 9 - 4,120 - - (4,120) -</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -22927,7 +22941,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Share-based compensation 9 - - - 187,087 - -</t>
+          <t>Expiry of broker warrants 9 - (2,013) - - 2,013 -</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -22976,8 +22990,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N221" s="5" t="n">
-        <v>0.187087</v>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -23003,7 +23019,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2024 47,633,283 $ 18,981,842 $ (70,566) $ 1,984,806 $ 226,862 $ - $</t>
+          <t>Share-based compensation 9 - - - 187,087 - -</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -23053,10 +23069,12 @@
         </is>
       </c>
       <c r="N222" s="5" t="n">
-        <v>10.424576</v>
-      </c>
-      <c r="O222" s="5" t="n">
-        <v>-10.698368</v>
+        <v>0.187087</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
@@ -23072,12 +23090,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reserve                       Debentures</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Interest and bank charges 7, 8</t>
+          <t>Balance, June 30, 2024 47,633,283 $ 18,981,842 $ (70,566) $ 1,984,806 $ 226,862 $ - $</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -23121,16 +23139,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M223" s="5" t="n">
-        <v>0.156865</v>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N223" s="5" t="n">
-        <v>0.180339</v>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.424576</v>
+      </c>
+      <c r="O223" s="5" t="n">
+        <v>-10.698368</v>
       </c>
       <c r="P223" t="inlineStr">
         <is>
@@ -23151,7 +23169,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Share-based compensation 6, 9, 15</t>
+          <t>Interest and bank charges 7, 8</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -23196,10 +23214,10 @@
         </is>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.485632</v>
+        <v>0.156865</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>0.394823</v>
+        <v>0.180339</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -23225,7 +23243,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Accretion expense 8</t>
+          <t>Share-based compensation 6, 9, 15</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -23270,10 +23288,10 @@
         </is>
       </c>
       <c r="M225" s="5" t="n">
-        <v>0.255782</v>
+        <v>0.485632</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>0.286432</v>
+        <v>0.394823</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -23299,7 +23317,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties and deferred exploration costs 4</t>
+          <t>Accretion expense 8</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -23344,10 +23362,10 @@
         </is>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.935984</v>
+        <v>0.255782</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.286432</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -23373,7 +23391,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of accounts payable 6</t>
+          <t>Impairment of mineral properties and deferred exploration costs 4</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -23417,13 +23435,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M227" s="5" t="n">
+        <v>0.935984</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>-0.485691</v>
+        <v>1e-06</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -23449,7 +23465,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Loss on sale of mineral property rights 4</t>
+          <t>Gain on extinguishment of accounts payable 6</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -23499,7 +23515,7 @@
         </is>
       </c>
       <c r="N228" s="5" t="n">
-        <v>0.084046</v>
+        <v>-0.485691</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -23525,7 +23541,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of loan 7</t>
+          <t>Loss on sale of mineral property rights 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -23569,13 +23585,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M229" s="5" t="n">
-        <v>-0.002208</v>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="5" t="n">
+        <v>0.084046</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -23601,7 +23617,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Income tax recovery 10</t>
+          <t>Gain on forgiveness of loan 7</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -23646,7 +23662,7 @@
         </is>
       </c>
       <c r="M230" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.002208</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -23672,12 +23688,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Weightedaverage number of common shares outstanding – basic</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Weightedaverage number of common shares outstanding – basic and diluted</t>
+          <t>Income tax recovery 10</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -23722,10 +23738,12 @@
         </is>
       </c>
       <c r="M231" s="5" t="n">
-        <v>26.641672</v>
-      </c>
-      <c r="N231" s="5" t="n">
-        <v>30.802797</v>
+        <v>0.012</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -23746,12 +23764,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Debentures</t>
+          <t>Weightedaverage number of common shares outstanding – basic</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2021 20,215,236 $ 8,780,386 $ (14,300) $ 956,038 $ - $ 378,542 $</t>
+          <t>Weightedaverage number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -23796,10 +23814,10 @@
         </is>
       </c>
       <c r="M232" s="5" t="n">
-        <v>4.182563</v>
+        <v>26.641672</v>
       </c>
       <c r="N232" s="5" t="n">
-        <v>-5.918103</v>
+        <v>30.802797</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -23825,7 +23843,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Units issued in private placements 9 3,991,670 2,948,850 (76,351) - 151,150 -</t>
+          <t>Balance, June 30, 2021 20,215,236 $ 8,780,386 $ (14,300) $ 956,038 $ - $ 378,542 $</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -23870,12 +23888,10 @@
         </is>
       </c>
       <c r="M233" s="5" t="n">
-        <v>3.023649</v>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.182563</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>-5.918103</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -23901,7 +23917,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Share issuance costs 9 - (92,907) - - - -</t>
+          <t>Units issued in private placements 9 3,991,670 2,948,850 (76,351) - 151,150 -</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -23946,7 +23962,7 @@
         </is>
       </c>
       <c r="M234" s="5" t="n">
-        <v>-0.092907</v>
+        <v>3.023649</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -23977,7 +23993,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Equity portion of convertible debenture 8 - - - - - 39,144</t>
+          <t>Share issuance costs 9 - (92,907) - - - -</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -24022,7 +24038,7 @@
         </is>
       </c>
       <c r="M235" s="5" t="n">
-        <v>0.039144</v>
+        <v>-0.092907</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -24053,7 +24069,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Broker warrants in connection with private placement 9, 15 - (25,060) - - 25,060 -</t>
+          <t>Equity portion of convertible debenture 8 - - - - - 39,144</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -24097,10 +24113,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M236" s="5" t="n">
+        <v>0.039144</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -24131,7 +24145,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Expiry of broker warrants 9 - 4,266 - - (4,266) -</t>
+          <t>Broker warrants in connection with private placement 9, 15 - (25,060) - - 25,060 -</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -24209,7 +24223,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Share-based compensation 9, 15 - - - 485,632 - -</t>
+          <t>Expiry of broker warrants 9 - 4,266 - - (4,266) -</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -24253,8 +24267,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M238" s="5" t="n">
-        <v>0.485632</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -24285,7 +24301,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Exercise of options 9 50,000 25,270 - (7,770) - -</t>
+          <t>Share-based compensation 9, 15 - - - 485,632 - -</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -24330,7 +24346,7 @@
         </is>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.485632</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -24361,7 +24377,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Exercise of warrants 9 4,310,360 1,530,628 - - - -</t>
+          <t>Exercise of options 9 50,000 25,270 - (7,770) - -</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -24406,7 +24422,7 @@
         </is>
       </c>
       <c r="M240" s="5" t="n">
-        <v>1.530628</v>
+        <v>0.0175</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -24437,7 +24453,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year 15 - - - - - -</t>
+          <t>Exercise of warrants 9 4,310,360 1,530,628 - - - -</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -24482,10 +24498,12 @@
         </is>
       </c>
       <c r="M241" s="5" t="n">
-        <v>-2.350109</v>
-      </c>
-      <c r="N241" s="5" t="n">
-        <v>-2.350109</v>
+        <v>1.530628</v>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -24511,7 +24529,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2022 (Restated - Note 15) 28,567,266 13,171,433 (90,651) 1,433,900 171,944 417,686</t>
+          <t>Net loss and comprehensive loss for the year 15 - - - - - -</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -24556,10 +24574,10 @@
         </is>
       </c>
       <c r="M242" s="5" t="n">
-        <v>6.8361</v>
+        <v>-2.350109</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>-8.268212</v>
+        <v>-2.350109</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -24585,7 +24603,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Units issued in private placement 9 2,610,018 1,571,632 (19,000) - 81,130 -</t>
+          <t>Balance, June 30, 2022 (Restated - Note 15) 28,567,266 13,171,433 (90,651) 1,433,900 171,944 417,686</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -24630,12 +24648,10 @@
         </is>
       </c>
       <c r="M243" s="5" t="n">
-        <v>1.633762</v>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.8361</v>
+      </c>
+      <c r="N243" s="5" t="n">
+        <v>-8.268212</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -24661,7 +24677,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Share issuance costs 9 - (6,825) - - - -</t>
+          <t>Units issued in private placement 9 2,610,018 1,571,632 (19,000) - 81,130 -</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -24706,7 +24722,7 @@
         </is>
       </c>
       <c r="M244" s="5" t="n">
-        <v>-0.006825</v>
+        <v>1.633762</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -24737,7 +24753,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Equity portion of convertible debenture 8 - 417,686 - - - (417,686)</t>
+          <t>Share issuance costs 9 - (6,825) - - - -</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -24781,10 +24797,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M245" s="5" t="n">
+        <v>-0.006825</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -24810,12 +24824,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of convertible debenture     8</t>
+          <t>Debentures</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of convertible debenture     8</t>
+          <t>Equity portion of convertible debenture 8 - 417,686 - - - (417,686)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -24859,8 +24873,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M246" s="5" t="n">
-        <v>1.975</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -24891,7 +24907,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Broker warrants in connection with private placement 9 - (2,013) - - 2,013 -</t>
+          <t>Shares issued on conversion of convertible debenture     8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -24935,10 +24951,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M247" s="5" t="n">
+        <v>1.975</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -24969,7 +24983,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Expiry of broker warrants 9 - 26,118 - - (26,118) -</t>
+          <t>Broker warrants in connection with private placement 9 - (2,013) - - 2,013 -</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -25047,7 +25061,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Share-based compensation 9 - - - 394,823 - -</t>
+          <t>Expiry of broker warrants 9 - 26,118 - - (26,118) -</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -25091,8 +25105,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M249" s="5" t="n">
-        <v>0.394823</v>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
@@ -25123,7 +25139,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Exercise of options 9 250,000 118,504 - (31,004) - -</t>
+          <t>Share-based compensation 9 - - - 394,823 - -</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -25168,7 +25184,7 @@
         </is>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.394823</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -25199,7 +25215,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Exercise of warrants 9 20,000 6,000 - - - -</t>
+          <t>Exercise of options 9 250,000 118,504 - (31,004) - -</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -25244,7 +25260,7 @@
         </is>
       </c>
       <c r="M251" s="5" t="n">
-        <v>0.006</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
@@ -25275,7 +25291,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - - - - -</t>
+          <t>Exercise of warrants 9 20,000 6,000 - - - -</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -25320,10 +25336,12 @@
         </is>
       </c>
       <c r="M252" s="5" t="n">
-        <v>-1.320323</v>
-      </c>
-      <c r="N252" s="5" t="n">
-        <v>-1.320323</v>
+        <v>0.006</v>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -25349,7 +25367,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 38,030,617 $ 17,277,535 $ (109,651) $ 1,797,719 $ 228,969 $ - $</t>
+          <t>Net loss and comprehensive loss for the year - - - - - -</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -25394,10 +25412,10 @@
         </is>
       </c>
       <c r="M253" s="5" t="n">
-        <v>9.606037000000001</v>
+        <v>-1.320323</v>
       </c>
       <c r="N253" s="5" t="n">
-        <v>-9.588535</v>
+        <v>-1.320323</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -25418,19 +25436,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued on conversion of convertible debenture     8</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Filing fees $</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance, June 30, 2023 38,030,617 $ 17,277,535 $ (109,651) $ 1,797,719 $ 228,969 $ - $</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -25461,21 +25475,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K254" s="5" t="n">
-        <v>0.019168</v>
-      </c>
-      <c r="L254" s="5" t="n">
-        <v>0.08676</v>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" s="5" t="n">
+        <v>9.606037000000001</v>
+      </c>
+      <c r="N254" s="5" t="n">
+        <v>-9.588535</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -25501,10 +25515,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Interest and charges 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Filing fees $</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -25536,10 +25554,10 @@
         </is>
       </c>
       <c r="K255" s="5" t="n">
-        <v>0.045915</v>
+        <v>0.019168</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>0.039586</v>
+        <v>0.08676</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -25575,7 +25593,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Accretion expense 9</t>
+          <t>Interest and charges 7, 8, 9</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -25609,13 +25627,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K256" s="5" t="n">
+        <v>0.045915</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>0.042045</v>
+        <v>0.039586</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -25651,14 +25667,10 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion expense 9</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -25684,14 +25696,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J257" s="5" t="n">
-        <v>0.0154</v>
-      </c>
-      <c r="K257" s="5" t="n">
-        <v>0.02</v>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L257" s="5" t="n">
-        <v>0.131741</v>
+        <v>0.042045</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -25727,10 +25743,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Share based compensation 10</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -25756,18 +25776,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J258" s="5" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>0.09331399999999999</v>
+        <v>0.131741</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
@@ -25803,7 +25819,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Income tax recovery 11</t>
+          <t>Share based compensation 10</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -25843,7 +25859,7 @@
         </is>
       </c>
       <c r="L259" s="5" t="n">
-        <v>0.14</v>
+        <v>0.09331399999999999</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -25874,15 +25890,19 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>– basic and diluted</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Income tax recovery 11</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -25913,11 +25933,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K260" s="5" t="n">
-        <v>2.577117</v>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L260" s="5" t="n">
-        <v>10.652103</v>
+        <v>0.14</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -25948,12 +25970,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Debentures</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2019 2,576,885 $ 4,193,934 $ (25,000) $ 842,508 $ - $</t>
+          <t>– basic and diluted</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -25988,10 +26010,10 @@
         </is>
       </c>
       <c r="K261" s="5" t="n">
-        <v>-0.278121</v>
+        <v>2.577117</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>-5.289563</v>
+        <v>10.652103</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -26027,7 +26049,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Subscriptions received 10 - - 25,000 - -</t>
+          <t>Balance, June 30, 2019 2,576,885 $ 4,193,934 $ (25,000) $ 842,508 $ - $</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -26062,12 +26084,10 @@
         </is>
       </c>
       <c r="K262" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.278121</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>-5.289563</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
@@ -26103,14 +26123,10 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Subscriptions received 10 - - 25,000 - -</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -26142,10 +26158,12 @@
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>-0.09774099999999999</v>
-      </c>
-      <c r="L263" s="5" t="n">
-        <v>-0.160065</v>
+        <v>0.025</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -26181,10 +26199,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2020 2,576,885 4,193,934 - 842,508 -</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -26216,10 +26238,10 @@
         </is>
       </c>
       <c r="K264" s="5" t="n">
-        <v>-0.413186</v>
+        <v>-0.09774099999999999</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>-5.449628</v>
+        <v>-0.160065</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
@@ -26255,7 +26277,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Shares issued in private placement 10 12,092,000 2,605,250 (14,300) - -</t>
+          <t>Balance, June 30, 2020 2,576,885 4,193,934 - 842,508 -</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -26290,12 +26312,10 @@
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>2.59095</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.413186</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>-5.449628</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
@@ -26331,7 +26351,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Shares isssued to settle loan payable 8, 10 350,000 70,000 - - -</t>
+          <t>Shares issued in private placement 10 12,092,000 2,605,250 (14,300) - -</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -26366,7 +26386,7 @@
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.59095</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -26407,7 +26427,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Share issuance costs 10 - (61,853) - - -</t>
+          <t>Shares isssued to settle loan payable 8, 10 350,000 70,000 - - -</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -26442,7 +26462,7 @@
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>-0.061853</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -26483,7 +26503,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Shares issued in acquisition of net profit interests 10, 8 5,125,000 1,981,000 - - -</t>
+          <t>Share issuance costs 10 - (61,853) - - -</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -26518,7 +26538,7 @@
         </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>1.981</v>
+        <v>-0.061853</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -26559,7 +26579,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Broker warrants in connection with private placement 10 - (20,215) - 20,215 -</t>
+          <t>Shares issued in acquisition of net profit interests 10, 8 5,125,000 1,981,000 - - -</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -26593,10 +26613,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K269" s="5" t="n">
+        <v>1.981</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -26637,7 +26655,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Share based compensation 10 - - - 93,314 -</t>
+          <t>Broker warrants in connection with private placement 10 - (20,215) - 20,215 -</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -26671,8 +26689,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K270" s="5" t="n">
-        <v>0.09331399999999999</v>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -26713,7 +26733,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Equity portion of convertible debenture 9 - - - - 378,542</t>
+          <t>Share based compensation 10 - - - 93,314 -</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -26748,7 +26768,7 @@
         </is>
       </c>
       <c r="K271" s="5" t="n">
-        <v>0.378542</v>
+        <v>0.09331399999999999</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -26789,7 +26809,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Exercise of warrants 10 61,350 12,270 - - -</t>
+          <t>Equity portion of convertible debenture 9 - - - - 378,542</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -26824,7 +26844,7 @@
         </is>
       </c>
       <c r="K272" s="5" t="n">
-        <v>0.01227</v>
+        <v>0.378542</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -26865,7 +26885,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2021 20,205,235 $ 8,780,386 $ (14,300) $ 956,037 $ 378,542 $</t>
+          <t>Exercise of warrants 10 61,350 12,270 - - -</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -26900,10 +26920,12 @@
         </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>4.182562</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>-5.918103</v>
+        <v>0.01227</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
@@ -26934,19 +26956,15 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Debentures</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Amortization $</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Balance, June 30, 2021 20,205,235 $ 8,780,386 $ (14,300) $ 956,037 $ 378,542 $</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -26972,18 +26990,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J274" s="5" t="n">
-        <v>0.001072</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>4.182562</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>-5.918103</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
@@ -27019,10 +27035,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Interest and charges 6, 7</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Amortization $</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -27049,10 +27069,12 @@
         </is>
       </c>
       <c r="J275" s="5" t="n">
-        <v>0.04528</v>
-      </c>
-      <c r="K275" s="5" t="n">
-        <v>0.045915</v>
+        <v>0.001072</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -27093,7 +27115,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Income on settlement of flow-through premium 8</t>
+          <t>Interest and charges 6, 7</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -27123,12 +27145,10 @@
         </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>0.003334</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.04528</v>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>0.045915</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -27164,12 +27184,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Weighted  average  number  of common  shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Weighted  average  number  of common  shares outstanding – basic and diluted</t>
+          <t>Income on settlement of flow-through premium 8</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -27199,10 +27219,12 @@
         </is>
       </c>
       <c r="J277" s="5" t="n">
-        <v>2.409547</v>
-      </c>
-      <c r="K277" s="5" t="n">
-        <v>2.576885</v>
+        <v>0.003334</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -27243,7 +27265,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2018 2,393,718 $ 4,121,988 $ - $ 842,508 $</t>
+          <t>Weighted  average  number  of common  shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -27273,10 +27295,10 @@
         </is>
       </c>
       <c r="J278" s="5" t="n">
-        <v>-0.203264</v>
+        <v>2.409547</v>
       </c>
       <c r="K278" s="5" t="n">
-        <v>-5.16776</v>
+        <v>2.576885</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -27317,7 +27339,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Shares issued in private placement 166,667 70,000 (25,000) -</t>
+          <t>Balance, June 30, 2018 2,393,718 $ 4,121,988 $ - $ 842,508 $</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -27347,12 +27369,10 @@
         </is>
       </c>
       <c r="J279" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.203264</v>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>-5.16776</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -27393,7 +27413,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability - (3,334) - -</t>
+          <t>Shares issued in private placement 166,667 70,000 (25,000) -</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -27423,7 +27443,7 @@
         </is>
       </c>
       <c r="J280" s="5" t="n">
-        <v>-0.003334</v>
+        <v>0.045</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -27469,7 +27489,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 16,500 5,280 - -</t>
+          <t>Flow-through share premium liability - (3,334) - -</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -27499,7 +27519,7 @@
         </is>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.00528</v>
+        <v>-0.003334</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -27545,14 +27565,10 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for exploration and evaluation assets 16,500 5,280 - -</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -27579,10 +27595,12 @@
         </is>
       </c>
       <c r="J282" s="5" t="n">
-        <v>-0.121803</v>
-      </c>
-      <c r="K282" s="5" t="n">
-        <v>-0.121803</v>
+        <v>0.00528</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -27623,10 +27641,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2019 2,576,885 4,193,934 (25,000) 842,508</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -27653,10 +27675,10 @@
         </is>
       </c>
       <c r="J283" s="5" t="n">
-        <v>-0.278121</v>
+        <v>-0.121803</v>
       </c>
       <c r="K283" s="5" t="n">
-        <v>-5.289563</v>
+        <v>-0.121803</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -27697,7 +27719,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Subscriptions received 8 - - 25,000 -</t>
+          <t>Balance, June 30, 2019 2,576,885 4,193,934 (25,000) 842,508</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -27727,12 +27749,10 @@
         </is>
       </c>
       <c r="J284" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.278121</v>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>-5.289563</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -27773,7 +27793,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2020 2,576,885 $ 4,193,934 $ - $ 842,508 $</t>
+          <t>Subscriptions received 8 - - 25,000 -</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -27803,10 +27823,12 @@
         </is>
       </c>
       <c r="J285" s="5" t="n">
-        <v>-0.413186</v>
-      </c>
-      <c r="K285" s="5" t="n">
-        <v>-5.449628</v>
+        <v>0.025</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -27842,41 +27864,45 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Weighted  average  number  of common  shares</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Amortization (Note 5) $</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E286" s="5" t="n">
-        <v>0.001263</v>
-      </c>
-      <c r="F286" s="5" t="n">
-        <v>0.000925</v>
-      </c>
-      <c r="G286" s="5" t="n">
-        <v>0.000677</v>
-      </c>
-      <c r="H286" s="5" t="n">
-        <v>0.000496</v>
-      </c>
-      <c r="I286" s="5" t="n">
-        <v>0.000282</v>
+          <t>Balance, June 30, 2020 2,576,885 $ 4,193,934 $ - $ 842,508 $</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J286" s="5" t="n">
-        <v>0.001072</v>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.413186</v>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>-5.449628</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -27917,31 +27943,31 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Amortization (Note 5) $</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">
-        <v>0.008832</v>
+        <v>0.001263</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.000925</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>0.006066</v>
+        <v>0.000677</v>
       </c>
       <c r="H287" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.000496</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.000282</v>
       </c>
       <c r="J287" s="5" t="n">
-        <v>0.018297</v>
+        <v>0.001072</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -27987,35 +28013,31 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Interest and finance fees (Notes 6 and 7)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="n">
+        <v>0.008832</v>
+      </c>
+      <c r="F288" s="5" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="G288" s="5" t="n">
+        <v>0.006066</v>
+      </c>
+      <c r="H288" s="5" t="n">
+        <v>0.0052</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>0.04</v>
+        <v>0.0052</v>
       </c>
       <c r="J288" s="5" t="n">
-        <v>0.04528</v>
+        <v>0.018297</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -28061,31 +28083,35 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E289" s="5" t="n">
-        <v>0.005848</v>
-      </c>
-      <c r="F289" s="5" t="n">
-        <v>0.010411</v>
-      </c>
-      <c r="G289" s="5" t="n">
-        <v>0.026945</v>
-      </c>
-      <c r="H289" s="5" t="n">
-        <v>0.014783</v>
+          <t>Interest and finance fees (Notes 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I289" s="5" t="n">
-        <v>0.020994</v>
+        <v>0.04</v>
       </c>
       <c r="J289" s="5" t="n">
-        <v>0.016964</v>
+        <v>0.04528</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -28131,7 +28157,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -28139,29 +28165,23 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E290" s="5" t="n">
+        <v>0.005848</v>
+      </c>
+      <c r="F290" s="5" t="n">
+        <v>0.010411</v>
+      </c>
+      <c r="G290" s="5" t="n">
+        <v>0.026945</v>
       </c>
       <c r="H290" s="5" t="n">
-        <v>0.015049</v>
+        <v>0.014783</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>0.053345</v>
+        <v>0.020994</v>
       </c>
       <c r="J290" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.016964</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -28207,12 +28227,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -28231,13 +28251,13 @@
         </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>0.044985</v>
+        <v>0.015049</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.030435</v>
+        <v>0.053345</v>
       </c>
       <c r="J291" s="5" t="n">
-        <v>0.028124</v>
+        <v>0.0154</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -28283,33 +28303,37 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E292" s="5" t="n">
-        <v>0.007377</v>
-      </c>
-      <c r="F292" s="5" t="n">
-        <v>0.008175999999999999</v>
-      </c>
-      <c r="G292" s="5" t="n">
-        <v>0.010669</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H292" s="5" t="n">
-        <v>0.008723</v>
+        <v>0.044985</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>0.001996</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030435</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>0.028124</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -28355,31 +28379,33 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Total general and administrative expenses</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
-        <v>-0.16567</v>
+        <v>0.007377</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>-0.160701</v>
+        <v>0.008175999999999999</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>-0.154158</v>
+        <v>0.010669</v>
       </c>
       <c r="H293" s="5" t="n">
-        <v>-0.129236</v>
+        <v>0.008723</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>-0.152252</v>
-      </c>
-      <c r="J293" s="5" t="n">
-        <v>-0.125137</v>
+        <v>0.001996</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -28425,37 +28451,31 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Income on settlement of flow-through premium (Note 8)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>-0.16567</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>-0.160701</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>-0.154158</v>
+      </c>
+      <c r="H294" s="5" t="n">
+        <v>-0.129236</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>-0.152252</v>
       </c>
       <c r="J294" s="5" t="n">
-        <v>0.003334</v>
+        <v>-0.125137</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -28501,7 +28521,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Write-off of amounts receivable</t>
+          <t>Income on settlement of flow-through premium (Note 8)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -28525,13 +28545,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I295" s="5" t="n">
-        <v>-0.026124</v>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="n">
+        <v>0.003334</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -28577,14 +28597,10 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of amounts receivable</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -28595,17 +28611,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G296" s="5" t="n">
-        <v>-0.154158</v>
-      </c>
-      <c r="H296" s="5" t="n">
-        <v>-0.129236</v>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I296" s="5" t="n">
-        <v>-0.178376</v>
-      </c>
-      <c r="J296" s="5" t="n">
-        <v>-0.121803</v>
+        <v>-0.026124</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -28651,12 +28673,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 9) $</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -28669,21 +28691,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G297" s="5" t="n">
+        <v>-0.154158</v>
+      </c>
+      <c r="H297" s="5" t="n">
+        <v>-0.129236</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.178376</v>
       </c>
       <c r="J297" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.121803</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
@@ -28729,10 +28747,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Basic and diluted loss per common share (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -28743,17 +28765,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G298" s="5" t="n">
-        <v>15.70822</v>
-      </c>
-      <c r="H298" s="5" t="n">
-        <v>18.267016</v>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I298" s="5" t="n">
-        <v>19.151605</v>
+        <v>-1e-08</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>19.276376</v>
+        <v>-1e-08</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -28794,12 +28820,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Shares   Share Capital      Receivable         Surplus           Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2017 19,151,605 $ 4,121,988 $ - $ 842,508 $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -28813,21 +28839,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G299" s="5" t="n">
+        <v>15.70822</v>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>18.267016</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>-0.024888</v>
+        <v>19.151605</v>
       </c>
       <c r="J299" s="5" t="n">
-        <v>-4.989384</v>
+        <v>19.276376</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -28873,14 +28895,10 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, June 30, 2017 19,151,605 $ 4,121,988 $ - $ 842,508 $</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -28902,10 +28920,10 @@
         </is>
       </c>
       <c r="I300" s="5" t="n">
-        <v>-0.178376</v>
+        <v>-0.024888</v>
       </c>
       <c r="J300" s="5" t="n">
-        <v>-0.178376</v>
+        <v>-4.989384</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -28951,10 +28969,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2018 19,151,605 4,121,988 - 842,508</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -28976,10 +28998,10 @@
         </is>
       </c>
       <c r="I301" s="5" t="n">
-        <v>-0.203264</v>
+        <v>-0.178376</v>
       </c>
       <c r="J301" s="5" t="n">
-        <v>-5.16776</v>
+        <v>-0.178376</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -29025,7 +29047,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Shares issued in private placement 1,333,334 70,000 (25,000) -</t>
+          <t>Balance, June 30, 2018 19,151,605 4,121,988 - 842,508</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -29050,12 +29072,10 @@
         </is>
       </c>
       <c r="I302" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.203264</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>-5.16776</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -29101,7 +29121,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability - (3,334) - -</t>
+          <t>Shares issued in private placement 1,333,334 70,000 (25,000) -</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -29126,7 +29146,7 @@
         </is>
       </c>
       <c r="I303" s="5" t="n">
-        <v>-0.003334</v>
+        <v>0.045</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -29177,7 +29197,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 132,000 5,280 - -</t>
+          <t>Flow-through share premium liability - (3,334) - -</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -29202,7 +29222,7 @@
         </is>
       </c>
       <c r="I304" s="5" t="n">
-        <v>0.00528</v>
+        <v>-0.003334</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -29253,7 +29273,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2019 20,616,939 $ 4,193,934 $ (25,000) $ 842,508 $</t>
+          <t>Shares issued for exploration and evaluation assets 132,000 5,280 - -</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -29278,10 +29298,12 @@
         </is>
       </c>
       <c r="I305" s="5" t="n">
-        <v>-0.278121</v>
-      </c>
-      <c r="J305" s="5" t="n">
-        <v>-5.289563</v>
+        <v>0.00528</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -29322,34 +29344,40 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Shares   Share Capital      Receivable         Surplus           Deficit            Total</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Interest (Note 6)</t>
+          <t>Balance, June 30, 2019 20,616,939 $ 4,193,934 $ (25,000) $ 842,508 $</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
-      <c r="E306" s="5" t="n">
-        <v>0.031811</v>
-      </c>
-      <c r="F306" s="5" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="G306" s="5" t="n">
-        <v>0.03875</v>
-      </c>
-      <c r="H306" s="5" t="n">
-        <v>0.04</v>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I306" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.278121</v>
+      </c>
+      <c r="J306" s="5" t="n">
+        <v>-5.289563</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -29395,32 +29423,24 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 8) $</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest (Note 6)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" s="5" t="n">
+        <v>0.031811</v>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>0.00625</v>
       </c>
       <c r="G307" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.03875</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.04</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.04</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -29466,15 +29486,19 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Shares    Share Capital         Surplus           Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2016 17,614,105 $ 4,004,486 $ 842,508 $</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Basic and diluted loss per common share (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -29485,16 +29509,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G308" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="H308" s="5" t="n">
-        <v>-0.013154</v>
+        <v>-1e-08</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>-4.860148</v>
+        <v>-1e-08</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -29545,7 +29567,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Private placement units issued 1,537,500 123,000 -</t>
+          <t>Balance, June 30, 2016 17,614,105 $ 4,004,486 $ 842,508 $</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -29559,16 +29581,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G309" s="5" t="n">
-        <v>0.123</v>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H309" s="5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013154</v>
+      </c>
+      <c r="I309" s="5" t="n">
+        <v>-4.860148</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -29619,7 +29641,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Share issue costs - (5,498) -</t>
+          <t>Private placement units issued 1,537,500 123,000 -</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -29633,13 +29655,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G310" s="5" t="n">
+        <v>0.123</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>0.005498</v>
+        <v>0.123</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -29695,14 +29715,10 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs - (5,498) -</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -29713,14 +29729,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G311" s="5" t="n">
-        <v>-0.154158</v>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H311" s="5" t="n">
-        <v>-0.129236</v>
-      </c>
-      <c r="I311" s="5" t="n">
-        <v>-0.129236</v>
+        <v>0.005498</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -29771,10 +29791,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2017 19,151,605 4,121,988 842,508</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -29785,16 +29809,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G312" s="5" t="n">
+        <v>-0.154158</v>
       </c>
       <c r="H312" s="5" t="n">
-        <v>-0.024888</v>
+        <v>-0.129236</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>-4.989384</v>
+        <v>-0.129236</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -29845,7 +29867,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2018 19,151,605 $ 4,121,988 $ 842,508 $</t>
+          <t>Balance, June 30, 2017 19,151,605 4,121,988 842,508</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -29865,10 +29887,10 @@
         </is>
       </c>
       <c r="H313" s="5" t="n">
-        <v>-0.203264</v>
+        <v>-0.024888</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>-5.16776</v>
+        <v>-4.989384</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -29914,35 +29936,35 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Shares    Share Capital         Surplus           Deficit            Total</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Professional fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E314" s="5" t="n">
-        <v>0.02319</v>
-      </c>
-      <c r="F314" s="5" t="n">
-        <v>0.017302</v>
-      </c>
-      <c r="G314" s="5" t="n">
-        <v>0.032656</v>
+          <t>Balance, June 30, 2018 19,151,605 $ 4,121,988 $ 842,508 $</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H314" s="5" t="n">
-        <v>0.044985</v>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.203264</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>-5.16776</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -29993,23 +30015,25 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 7)</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Professional fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
-        <v>0.002708</v>
+        <v>0.02319</v>
       </c>
       <c r="F315" s="5" t="n">
-        <v>0.112437</v>
+        <v>0.017302</v>
       </c>
       <c r="G315" s="5" t="n">
-        <v>0.038395</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032656</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>0.044985</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -30060,30 +30084,28 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Shares    Share Capital         Surplus           Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2015 14,281,105 $ 3,672,921 $ 819,053 $</t>
+          <t>Share-based compensation (Note 7)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E316" s="5" t="n">
+        <v>0.002708</v>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>0.112437</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>-0.214016</v>
-      </c>
-      <c r="H316" s="5" t="n">
-        <v>-4.70599</v>
+        <v>0.038395</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -30139,7 +30161,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 23,455</t>
+          <t>Balance, June 30, 2015 14,281,105 $ 3,672,921 $ 819,053 $</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -30154,12 +30176,10 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>0.023455</v>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.214016</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-4.70599</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -30215,7 +30235,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Private placement units issued 3,250,000 325,000 -</t>
+          <t>Share-based compensation - - 23,455</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -30230,7 +30250,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>0.325</v>
+        <v>0.023455</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -30291,7 +30311,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Share issue costs - (8,375) -</t>
+          <t>Private placement units issued 3,250,000 325,000 -</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -30306,7 +30326,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>-0.008375</v>
+        <v>0.325</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -30367,7 +30387,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Bonus shares issued 83,000 14,940 -</t>
+          <t>Share issue costs - (8,375) -</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -30382,7 +30402,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>0.01494</v>
+        <v>-0.008375</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -30443,7 +30463,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2016 17,614,105 4,004,486 842,508</t>
+          <t>Bonus shares issued 83,000 14,940 -</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -30458,10 +30478,12 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>-0.013154</v>
-      </c>
-      <c r="H321" s="5" t="n">
-        <v>-4.860148</v>
+        <v>0.01494</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -30517,7 +30539,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Balance, June 30, 2016 17,614,105 4,004,486 842,508</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -30532,10 +30554,10 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>-0.005498</v>
+        <v>-0.013154</v>
       </c>
       <c r="H322" s="5" t="n">
-        <v>-0.005498</v>
+        <v>-4.860148</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -30591,7 +30613,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2017 19,151,605 $ 4,121,988 $ 842,508 $</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -30606,10 +30628,10 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>-0.024888</v>
+        <v>-0.005498</v>
       </c>
       <c r="H323" s="5" t="n">
-        <v>-4.989384</v>
+        <v>-0.005498</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -30660,12 +30682,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Shares    Share Capital         Surplus           Deficit            Total</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Gain on debt forgiveness (Note 6)</t>
+          <t>Balance, June 30, 2017 19,151,605 $ 4,121,988 $ 842,508 $</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -30674,18 +30696,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F324" s="5" t="n">
-        <v>0.339518</v>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>-0.024888</v>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>-4.989384</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -30741,22 +30761,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E325" s="5" t="n">
-        <v>-0.16567</v>
+          <t>Gain on debt forgiveness (Note 6)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F325" s="5" t="n">
-        <v>0.178817</v>
-      </c>
-      <c r="G325" s="5" t="n">
-        <v>-0.154158</v>
+        <v>0.339518</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -30817,22 +30837,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Basic and diluted income (loss) per common share (Note 8) $</t>
+          <t>Comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.16567</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.178817</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.154158</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -30893,22 +30913,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic</t>
+          <t>Basic and diluted income (loss) per common share (Note 8) $</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E327" s="5" t="n">
-        <v>14.281105</v>
+        <v>-1e-08</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>14.281105</v>
+        <v>1e-08</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>15.70822</v>
+        <v>-1e-08</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -30969,19 +30989,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - diluted</t>
+          <t>Weighted average number of common shares outstanding – basic</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
         <v>14.281105</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>15.931105</v>
+        <v>14.281105</v>
       </c>
       <c r="G328" s="5" t="n">
         <v>15.70822</v>
@@ -31040,25 +31060,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Shares    Share Capital          Surplus           Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2014 14,281,105 $ 3,672,921 $ 706,616 $</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding - diluted</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="n">
+        <v>14.281105</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>-0.50527</v>
+        <v>15.931105</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>-4.884807</v>
+        <v>15.70822</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -31119,20 +31141,20 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 112,437</t>
+          <t>Balance, June 30, 2014 14,281,105 $ 3,672,921 $ 706,616 $</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" s="5" t="n">
-        <v>0.112437</v>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.112437</v>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.50527</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>-4.884807</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -31193,22 +31215,20 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Net income for the year - - -</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 112,437</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" s="5" t="n">
-        <v>0.178817</v>
+        <v>0.112437</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>0.178817</v>
-      </c>
-      <c r="G331" s="5" t="n">
-        <v>0.178817</v>
+        <v>0.112437</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
@@ -31269,20 +31289,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2015 14,281,105 3,672,921 819,053</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income for the year - - -</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="n">
+        <v>0.178817</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.214016</v>
+        <v>0.178817</v>
       </c>
       <c r="G332" s="5" t="n">
-        <v>-4.70599</v>
+        <v>0.178817</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
@@ -31343,7 +31365,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 23,455</t>
+          <t>Balance, June 30, 2015 14,281,105 3,672,921 819,053</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -31353,12 +31375,10 @@
         </is>
       </c>
       <c r="F333" s="5" t="n">
-        <v>0.023455</v>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.214016</v>
+      </c>
+      <c r="G333" s="5" t="n">
+        <v>-4.70599</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -31419,7 +31439,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Private placement units issued 3,250,000 325,000 -</t>
+          <t>Share-based compensation - - 23,455</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -31429,7 +31449,7 @@
         </is>
       </c>
       <c r="F334" s="5" t="n">
-        <v>0.325</v>
+        <v>0.023455</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -31495,7 +31515,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Share issue costs - (8,375) -</t>
+          <t>Private placement units issued 3,250,000 325,000 -</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -31505,7 +31525,7 @@
         </is>
       </c>
       <c r="F335" s="5" t="n">
-        <v>-0.008375</v>
+        <v>0.325</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -31571,7 +31591,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bonus shares issued 83,000 14,940 -</t>
+          <t>Share issue costs - (8,375) -</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -31581,7 +31601,7 @@
         </is>
       </c>
       <c r="F336" s="5" t="n">
-        <v>0.01494</v>
+        <v>-0.008375</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -31647,22 +31667,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E337" s="5" t="n">
-        <v>-0.16567</v>
+          <t>Bonus shares issued 83,000 14,940 -</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F337" s="5" t="n">
-        <v>-0.154158</v>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>-0.154158</v>
+        <v>0.01494</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -31723,20 +31743,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2016 17,614,105 $ 4,004,486 $ 842,508 $</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="n">
+        <v>-0.16567</v>
       </c>
       <c r="F338" s="5" t="n">
-        <v>-0.013154</v>
+        <v>-0.154158</v>
       </c>
       <c r="G338" s="5" t="n">
-        <v>-4.860148</v>
+        <v>-0.154158</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -31792,31 +31814,25 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Shares    Share Capital          Surplus           Deficit            Total</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Management fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E339" s="5" t="n">
-        <v>0.06825000000000001</v>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, June 30, 2016 17,614,105 $ 4,004,486 $ 842,508 $</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>-0.013154</v>
+      </c>
+      <c r="G339" s="5" t="n">
+        <v>-4.860148</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
@@ -31877,16 +31893,16 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Management fees (Note 6)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E340" s="5" t="n">
-        <v>0.013753</v>
+        <v>0.06825000000000001</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31957,12 +31973,16 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
-        <v>0.002638</v>
+        <v>0.013753</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32028,20 +32048,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Shares    Share Capital          Surplus           Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2013 14,281,105 $ 3,672,921 $ 703,908 $</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" s="5" t="n">
-        <v>-0.342308</v>
-      </c>
-      <c r="F342" s="5" t="n">
-        <v>-4.719137</v>
+        <v>0.002638</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -32107,17 +32129,15 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 2,708</t>
+          <t>Balance, June 30, 2013 14,281,105 $ 3,672,921 $ 703,908 $</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" s="5" t="n">
-        <v>0.107633</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.342308</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>-4.719137</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -32183,15 +32203,17 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2014 14,281,105 3,672,921 706,616</t>
+          <t>Share-based compensation - - 2,708</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" s="5" t="n">
-        <v>-0.50527</v>
-      </c>
-      <c r="F344" s="5" t="n">
-        <v>-4.884807</v>
+        <v>0.107633</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -32257,62 +32279,136 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2015 14,281,105 $ 3,672,921 $ 819,053 $</t>
+          <t>Balance, June 30, 2014 14,281,105 3,672,921 706,616</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" s="5" t="n">
+        <v>-0.50527</v>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>-4.884807</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Shares    Share Capital          Surplus           Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2015 14,281,105 $ 3,672,921 $ 819,053 $</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" s="5" t="n">
         <v>-0.214016</v>
       </c>
-      <c r="F345" s="5" t="n">
+      <c r="F346" s="5" t="n">
         <v>-4.70599</v>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P345" t="inlineStr">
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
         <is>
           <t>-</t>
         </is>
